--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0003T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0003T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.55178669981664</v>
+        <v>6.914665338720204</v>
       </c>
       <c r="D2" t="n">
-        <v>38.94873477780766</v>
+        <v>6.329169401393744</v>
       </c>
       <c r="E2" t="n">
-        <v>25.17700993266272</v>
+        <v>4.091264114057692</v>
       </c>
       <c r="F2" t="n">
-        <v>28.87743145768845</v>
+        <v>4.692582611874374</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.18234655961855</v>
+        <v>4.904631315938015</v>
       </c>
       <c r="D3" t="n">
-        <v>17.95274788236326</v>
+        <v>2.91732153088403</v>
       </c>
       <c r="E3" t="n">
-        <v>25.17700993266272</v>
+        <v>4.091264114057692</v>
       </c>
       <c r="F3" t="n">
-        <v>28.87743145768845</v>
+        <v>4.692582611874374</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>63.48399538001097</v>
+        <v>10.31614924925178</v>
       </c>
       <c r="D4" t="n">
-        <v>61.18462112623261</v>
+        <v>9.942500933012798</v>
       </c>
       <c r="E4" t="n">
-        <v>25.17700993266272</v>
+        <v>4.091264114057692</v>
       </c>
       <c r="F4" t="n">
-        <v>28.87743145768845</v>
+        <v>4.692582611874374</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>103.7327608093748</v>
+        <v>16.8565736315234</v>
       </c>
       <c r="D5" t="n">
-        <v>104.4217898235724</v>
+        <v>16.96854084633052</v>
       </c>
       <c r="E5" t="n">
-        <v>25.17700993266272</v>
+        <v>4.091264114057692</v>
       </c>
       <c r="F5" t="n">
-        <v>28.87743145768845</v>
+        <v>4.692582611874374</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>51.98892926330316</v>
+        <v>8.448201005286764</v>
       </c>
       <c r="D6" t="n">
-        <v>46.95245842931665</v>
+        <v>7.629774494763955</v>
       </c>
       <c r="E6" t="n">
-        <v>25.17700993266272</v>
+        <v>4.091264114057692</v>
       </c>
       <c r="F6" t="n">
-        <v>28.87743145768845</v>
+        <v>4.692582611874374</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
